--- a/Team-Data/2011-12/3-30-2011-12.xlsx
+++ b/Team-Data/2011-12/3-30-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,49 +728,49 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
         <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.585</v>
+        <v>0.577</v>
       </c>
       <c r="H2" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I2" t="n">
         <v>36.1</v>
       </c>
       <c r="J2" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L2" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M2" t="n">
         <v>19.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.37</v>
+        <v>0.373</v>
       </c>
       <c r="O2" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.731</v>
+        <v>0.728</v>
       </c>
       <c r="R2" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S2" t="n">
         <v>31.2</v>
@@ -727,25 +794,25 @@
         <v>5.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>9</v>
@@ -760,7 +827,7 @@
         <v>16</v>
       </c>
       <c r="AK2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -787,16 +854,16 @@
         <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
@@ -808,7 +875,7 @@
         <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
         <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>0.569</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.457</v>
@@ -873,67 +940,67 @@
         <v>15.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O3" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="P3" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R3" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="S3" t="n">
         <v>30.4</v>
       </c>
       <c r="T3" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="U3" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
         <v>7.2</v>
       </c>
       <c r="X3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
         <v>20.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
         <v>11</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
         <v>22</v>
@@ -942,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL3" t="n">
         <v>23</v>
@@ -957,10 +1024,10 @@
         <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
@@ -975,16 +1042,16 @@
         <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
         <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -996,7 +1063,7 @@
         <v>27</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -1025,67 +1092,67 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>0.143</v>
+        <v>0.146</v>
       </c>
       <c r="H4" t="n">
         <v>48.1</v>
       </c>
       <c r="I4" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="J4" t="n">
-        <v>80.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.298</v>
+        <v>0.299</v>
       </c>
       <c r="O4" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R4" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S4" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="T4" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="U4" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
         <v>14.2</v>
       </c>
       <c r="W4" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y4" t="n">
         <v>5.9</v>
@@ -1103,7 +1170,7 @@
         <v>-12.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1121,7 +1188,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
@@ -1139,22 +1206,22 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1166,7 +1233,7 @@
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1274,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>0.792</v>
+        <v>0.788</v>
       </c>
       <c r="H5" t="n">
         <v>48.1</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.384</v>
       </c>
       <c r="O5" t="n">
         <v>15.6</v>
@@ -1246,43 +1313,43 @@
         <v>21.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.727</v>
+        <v>0.725</v>
       </c>
       <c r="R5" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="S5" t="n">
         <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="U5" t="n">
         <v>23.1</v>
       </c>
       <c r="V5" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y5" t="n">
         <v>5.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="AA5" t="n">
         <v>17.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.2</v>
+        <v>97.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1300,13 +1367,13 @@
         <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL5" t="n">
         <v>18</v>
@@ -1315,10 +1382,10 @@
         <v>19</v>
       </c>
       <c r="AN5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
@@ -1327,7 +1394,7 @@
         <v>25</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
         <v>6</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.347</v>
+        <v>0.354</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1407,7 +1474,7 @@
         <v>34.4</v>
       </c>
       <c r="J6" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
         <v>0.424</v>
@@ -1419,16 +1486,16 @@
         <v>19.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.705</v>
+        <v>0.708</v>
       </c>
       <c r="R6" t="n">
         <v>12.9</v>
@@ -1440,43 +1507,43 @@
         <v>43</v>
       </c>
       <c r="U6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-5.7</v>
+        <v>-5.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF6" t="n">
         <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="n">
         <v>16</v>
@@ -1485,13 +1552,13 @@
         <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM6" t="n">
         <v>16</v>
@@ -1524,10 +1591,10 @@
         <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1539,10 +1606,10 @@
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
         <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J7" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L7" t="n">
         <v>7.5</v>
@@ -1604,34 +1671,34 @@
         <v>0.334</v>
       </c>
       <c r="O7" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P7" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S7" t="n">
         <v>32.4</v>
       </c>
       <c r="T7" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U7" t="n">
         <v>21.2</v>
       </c>
       <c r="V7" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y7" t="n">
         <v>4.2</v>
@@ -1640,10 +1707,10 @@
         <v>19.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AC7" t="n">
         <v>1.4</v>
@@ -1652,49 +1719,49 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>14</v>
       </c>
       <c r="AI7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
         <v>14</v>
@@ -1703,7 +1770,7 @@
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1724,7 +1791,7 @@
         <v>19</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" t="n">
         <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.538</v>
+        <v>0.529</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
@@ -1771,19 +1838,19 @@
         <v>38.3</v>
       </c>
       <c r="J8" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.321</v>
+        <v>0.324</v>
       </c>
       <c r="O8" t="n">
         <v>20.5</v>
@@ -1795,46 +1862,46 @@
         <v>0.738</v>
       </c>
       <c r="R8" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T8" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U8" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
         <v>22.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD8" t="n">
         <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
@@ -1846,16 +1913,16 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK8" t="n">
         <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1876,28 +1943,28 @@
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
         <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
         <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>0.353</v>
+        <v>0.36</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="J9" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
@@ -1965,31 +2032,31 @@
         <v>13.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O9" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P9" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R9" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S9" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T9" t="n">
         <v>39.8</v>
       </c>
       <c r="U9" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="V9" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W9" t="n">
         <v>7.1</v>
@@ -1998,22 +2065,22 @@
         <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z9" t="n">
         <v>19.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>89.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.7</v>
+        <v>-5.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
         <v>28</v>
@@ -2043,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
         <v>14</v>
@@ -2067,13 +2134,13 @@
         <v>27</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -2117,67 +2184,67 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.408</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J10" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L10" t="n">
         <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O10" t="n">
         <v>15.3</v>
       </c>
       <c r="P10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R10" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T10" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="U10" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V10" t="n">
         <v>13.9</v>
       </c>
       <c r="W10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y10" t="n">
         <v>4.5</v>
@@ -2186,16 +2253,16 @@
         <v>21.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC10" t="n">
         <v>-2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2210,25 +2277,25 @@
         <v>17</v>
       </c>
       <c r="AI10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK10" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>7</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP10" t="n">
         <v>29</v>
@@ -2240,7 +2307,7 @@
         <v>29</v>
       </c>
       <c r="AS10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
         <v>28</v>
@@ -2249,10 +2316,10 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.538</v>
+        <v>0.529</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
@@ -2317,19 +2384,19 @@
         <v>37.6</v>
       </c>
       <c r="J11" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L11" t="n">
         <v>6.9</v>
       </c>
       <c r="M11" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O11" t="n">
         <v>15.9</v>
@@ -2338,13 +2405,13 @@
         <v>20.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.788</v>
+        <v>0.789</v>
       </c>
       <c r="R11" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S11" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T11" t="n">
         <v>42.2</v>
@@ -2359,13 +2426,13 @@
         <v>7.3</v>
       </c>
       <c r="X11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y11" t="n">
         <v>5.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA11" t="n">
         <v>18.5</v>
@@ -2374,13 +2441,13 @@
         <v>98.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD11" t="n">
         <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
         <v>14</v>
@@ -2395,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
         <v>11</v>
@@ -2413,10 +2480,10 @@
         <v>19</v>
       </c>
       <c r="AP11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
         <v>15</v>
@@ -2428,22 +2495,22 @@
         <v>15</v>
       </c>
       <c r="AU11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV11" t="n">
         <v>16</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>17</v>
       </c>
       <c r="AW11" t="n">
         <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY11" t="n">
         <v>19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -2559,28 +2626,28 @@
         <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AE12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
         <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>23</v>
       </c>
       <c r="AJ12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>19</v>
@@ -2601,22 +2668,22 @@
         <v>7</v>
       </c>
       <c r="AR12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT12" t="n">
         <v>8</v>
       </c>
-      <c r="AS12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9</v>
-      </c>
       <c r="AU12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV12" t="n">
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.588</v>
+        <v>0.58</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L13" t="n">
         <v>7.5</v>
@@ -2693,28 +2760,28 @@
         <v>21.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O13" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P13" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S13" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T13" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="n">
         <v>13.4</v>
@@ -2726,10 +2793,10 @@
         <v>4.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AA13" t="n">
         <v>21.7</v>
@@ -2741,10 +2808,10 @@
         <v>1.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2759,13 +2826,13 @@
         <v>14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM13" t="n">
         <v>5</v>
@@ -2783,25 +2850,25 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV13" t="n">
         <v>3</v>
       </c>
       <c r="AW13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY13" t="n">
         <v>6</v>
@@ -2816,7 +2883,7 @@
         <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
         <v>6</v>
@@ -2938,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="AI14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2956,7 +3023,7 @@
         <v>28</v>
       </c>
       <c r="AO14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -2977,7 +3044,7 @@
         <v>11</v>
       </c>
       <c r="AV14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
@@ -2992,7 +3059,7 @@
         <v>3</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
         <v>17</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
         <v>27</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.551</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3045,46 +3112,46 @@
         <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="M15" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.317</v>
+        <v>0.324</v>
       </c>
       <c r="O15" t="n">
         <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="S15" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="T15" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U15" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V15" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W15" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="X15" t="n">
         <v>5.2</v>
@@ -3093,28 +3160,28 @@
         <v>5.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA15" t="n">
         <v>19.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH15" t="n">
         <v>9</v>
@@ -3123,10 +3190,10 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AL15" t="n">
         <v>29</v>
@@ -3135,31 +3202,31 @@
         <v>29</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT15" t="n">
         <v>17</v>
       </c>
-      <c r="AR15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>16</v>
-      </c>
       <c r="AU15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
@@ -3171,7 +3238,7 @@
         <v>23</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
         <v>15</v>
@@ -3180,7 +3247,7 @@
         <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -3209,34 +3276,34 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.74</v>
+        <v>0.735</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J16" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.482</v>
+        <v>0.48</v>
       </c>
       <c r="L16" t="n">
         <v>5.7</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N16" t="n">
         <v>0.378</v>
@@ -3248,22 +3315,22 @@
         <v>25.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R16" t="n">
         <v>10.1</v>
       </c>
       <c r="S16" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T16" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
         <v>9.1</v>
@@ -3275,19 +3342,19 @@
         <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB16" t="n">
-        <v>101.3</v>
+        <v>101</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3326,19 +3393,19 @@
         <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
@@ -3353,13 +3420,13 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
         <v>7</v>
       </c>
       <c r="BB16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC16" t="n">
         <v>2</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -3391,61 +3458,61 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
         <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>0.471</v>
+        <v>0.46</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>37.7</v>
+        <v>37.4</v>
       </c>
       <c r="J17" t="n">
         <v>85.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M17" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.347</v>
+        <v>0.343</v>
       </c>
       <c r="O17" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.787</v>
+        <v>0.79</v>
       </c>
       <c r="R17" t="n">
         <v>12.6</v>
       </c>
       <c r="S17" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="T17" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U17" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V17" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W17" t="n">
         <v>8.199999999999999</v>
@@ -3454,52 +3521,52 @@
         <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM17" t="n">
         <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
         <v>18</v>
@@ -3508,43 +3575,43 @@
         <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR17" t="n">
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
         <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA17" t="n">
         <v>19</v>
       </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA17" t="n">
+      <c r="BB17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC17" t="n">
         <v>20</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>0.472</v>
+        <v>0.481</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="O18" t="n">
         <v>19.6</v>
@@ -3612,7 +3679,7 @@
         <v>25.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R18" t="n">
         <v>12.6</v>
@@ -3624,31 +3691,31 @@
         <v>44.6</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V18" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W18" t="n">
         <v>7</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA18" t="n">
         <v>22</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="AD18" t="n">
         <v>1</v>
@@ -3657,7 +3724,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
         <v>19</v>
@@ -3669,10 +3736,10 @@
         <v>19</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
         <v>9</v>
@@ -3702,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
@@ -3723,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
         <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,7 +3840,7 @@
         <v>33.8</v>
       </c>
       <c r="J19" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0.424</v>
@@ -3785,16 +3852,16 @@
         <v>23.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P19" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R19" t="n">
         <v>12.1</v>
@@ -3803,16 +3870,16 @@
         <v>28.1</v>
       </c>
       <c r="T19" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U19" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V19" t="n">
         <v>15.3</v>
       </c>
       <c r="W19" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="X19" t="n">
         <v>4.1</v>
@@ -3821,28 +3888,28 @@
         <v>4.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA19" t="n">
         <v>19.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.8</v>
+        <v>-6</v>
       </c>
       <c r="AD19" t="n">
         <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH19" t="n">
         <v>28</v>
@@ -3863,16 +3930,16 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
         <v>10</v>
@@ -3887,19 +3954,19 @@
         <v>24</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
         <v>16</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
         <v>28</v>
@@ -4048,28 +4115,28 @@
         <v>22</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW20" t="n">
         <v>22</v>
@@ -4078,7 +4145,7 @@
         <v>20</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E21" t="n">
         <v>26</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.438</v>
@@ -4146,37 +4213,37 @@
         <v>7.1</v>
       </c>
       <c r="M21" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.315</v>
+        <v>0.314</v>
       </c>
       <c r="O21" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P21" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R21" t="n">
         <v>11.6</v>
       </c>
       <c r="S21" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T21" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="U21" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
         <v>16.6</v>
       </c>
       <c r="W21" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X21" t="n">
         <v>4.3</v>
@@ -4188,13 +4255,13 @@
         <v>21.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
         <v>6</v>
@@ -4209,7 +4276,7 @@
         <v>17</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4218,13 +4285,13 @@
         <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
         <v>10</v>
       </c>
       <c r="AM21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN21" t="n">
         <v>27</v>
@@ -4242,13 +4309,13 @@
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,7 +4461,7 @@
         <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>25</v>
@@ -4427,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>28</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" t="n">
         <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G23" t="n">
-        <v>0.615</v>
+        <v>0.627</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
@@ -4510,34 +4577,34 @@
         <v>10.3</v>
       </c>
       <c r="M23" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O23" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P23" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q23" t="n">
         <v>0.643</v>
       </c>
       <c r="R23" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U23" t="n">
         <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W23" t="n">
         <v>6.7</v>
@@ -4549,16 +4616,16 @@
         <v>4.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AA23" t="n">
         <v>20.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD23" t="n">
         <v>6</v>
@@ -4573,7 +4640,7 @@
         <v>5</v>
       </c>
       <c r="AH23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -4582,7 +4649,7 @@
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4606,13 +4673,13 @@
         <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV23" t="n">
         <v>26</v>
@@ -4621,22 +4688,22 @@
         <v>28</v>
       </c>
       <c r="AX23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
         <v>28</v>
       </c>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.549</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J24" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L24" t="n">
         <v>5.5</v>
@@ -4695,13 +4762,13 @@
         <v>14.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O24" t="n">
         <v>12.9</v>
       </c>
       <c r="P24" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="Q24" t="n">
         <v>0.733</v>
@@ -4710,10 +4777,10 @@
         <v>10.6</v>
       </c>
       <c r="S24" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T24" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U24" t="n">
         <v>21.8</v>
@@ -4722,52 +4789,52 @@
         <v>11</v>
       </c>
       <c r="W24" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
         <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="AA24" t="n">
         <v>16.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AJ24" t="n">
         <v>4</v>
       </c>
       <c r="AK24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
@@ -4791,10 +4858,10 @@
         <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
@@ -4806,16 +4873,16 @@
         <v>17</v>
       </c>
       <c r="AY24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC24" t="n">
         <v>4</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>-0.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>18</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG25" t="n">
         <v>18</v>
@@ -4940,7 +5007,7 @@
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
         <v>11</v>
@@ -4949,7 +5016,7 @@
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
         <v>17</v>
@@ -4964,16 +5031,16 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="n">
         <v>5</v>
@@ -4997,7 +5064,7 @@
         <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC25" t="n">
         <v>21</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -5029,67 +5096,67 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" t="n">
         <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462</v>
+        <v>0.471</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L26" t="n">
         <v>6.9</v>
       </c>
       <c r="M26" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O26" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P26" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="R26" t="n">
         <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V26" t="n">
         <v>14.2</v>
       </c>
       <c r="W26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y26" t="n">
         <v>4.7</v>
@@ -5098,10 +5165,10 @@
         <v>19.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0.8</v>
@@ -5113,25 +5180,25 @@
         <v>20</v>
       </c>
       <c r="AF26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG26" t="n">
         <v>20</v>
       </c>
-      <c r="AG26" t="n">
-        <v>21</v>
-      </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
       </c>
       <c r="AJ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL26" t="n">
         <v>12</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>11</v>
       </c>
       <c r="AM26" t="n">
         <v>9</v>
@@ -5140,7 +5207,7 @@
         <v>18</v>
       </c>
       <c r="AO26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP26" t="n">
         <v>17</v>
@@ -5149,10 +5216,10 @@
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5167,16 +5234,16 @@
         <v>9</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
         <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>0.353</v>
+        <v>0.34</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J27" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.43</v>
@@ -5238,73 +5305,73 @@
         <v>6.4</v>
       </c>
       <c r="M27" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="O27" t="n">
         <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.748</v>
+        <v>0.75</v>
       </c>
       <c r="R27" t="n">
         <v>13.7</v>
       </c>
       <c r="S27" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T27" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U27" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V27" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W27" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y27" t="n">
         <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.4</v>
+        <v>-5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
@@ -5319,7 +5386,7 @@
         <v>10</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>10</v>
@@ -5328,43 +5395,43 @@
         <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW27" t="n">
         <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY27" t="n">
         <v>28</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5483,13 +5550,13 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK28" t="n">
         <v>4</v>
@@ -5498,13 +5565,13 @@
         <v>2</v>
       </c>
       <c r="AM28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
         <v>21</v>
@@ -5519,7 +5586,7 @@
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5528,10 +5595,10 @@
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY28" t="n">
         <v>17</v>
@@ -5543,7 +5610,7 @@
         <v>21</v>
       </c>
       <c r="BB28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -5575,64 +5642,64 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E29" t="n">
         <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" t="n">
-        <v>0.327</v>
+        <v>0.333</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J29" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L29" t="n">
         <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O29" t="n">
         <v>16.9</v>
       </c>
       <c r="P29" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
       </c>
       <c r="S29" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="T29" t="n">
-        <v>41.3</v>
+        <v>41.6</v>
       </c>
       <c r="U29" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
         <v>15.3</v>
       </c>
       <c r="W29" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X29" t="n">
         <v>5</v>
@@ -5641,28 +5708,28 @@
         <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.7</v>
+        <v>91.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
         <v>6</v>
       </c>
       <c r="AE29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF29" t="n">
         <v>26</v>
       </c>
       <c r="AG29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
         <v>8</v>
@@ -5677,7 +5744,7 @@
         <v>19</v>
       </c>
       <c r="AL29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM29" t="n">
         <v>20</v>
@@ -5689,19 +5756,19 @@
         <v>14</v>
       </c>
       <c r="AP29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
         <v>23</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AU29" t="n">
         <v>12</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" t="n">
         <v>27</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.519</v>
+        <v>0.529</v>
       </c>
       <c r="H30" t="n">
         <v>48.9</v>
       </c>
       <c r="I30" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J30" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L30" t="n">
         <v>3.8</v>
@@ -5787,25 +5854,25 @@
         <v>12.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.307</v>
+        <v>0.308</v>
       </c>
       <c r="O30" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="P30" t="n">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R30" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="S30" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T30" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="U30" t="n">
         <v>21.7</v>
@@ -5820,16 +5887,16 @@
         <v>5.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5838,25 +5905,25 @@
         <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
       </c>
       <c r="AI30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ30" t="n">
         <v>3</v>
       </c>
       <c r="AK30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -5868,19 +5935,19 @@
         <v>29</v>
       </c>
       <c r="AO30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP30" t="n">
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT30" t="n">
         <v>4</v>
@@ -5889,7 +5956,7 @@
         <v>10</v>
       </c>
       <c r="AV30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
@@ -5907,7 +5974,7 @@
         <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC30" t="n">
         <v>19</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
@@ -5939,64 +6006,64 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>39</v>
       </c>
       <c r="G31" t="n">
-        <v>0.235</v>
+        <v>0.22</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="K31" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L31" t="n">
         <v>5.1</v>
       </c>
       <c r="M31" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N31" t="n">
-        <v>0.317</v>
+        <v>0.315</v>
       </c>
       <c r="O31" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R31" t="n">
         <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U31" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X31" t="n">
         <v>6.6</v>
@@ -6005,19 +6072,19 @@
         <v>4.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.7</v>
+        <v>-7.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6032,13 +6099,13 @@
         <v>26</v>
       </c>
       <c r="AI31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6047,10 +6114,10 @@
         <v>21</v>
       </c>
       <c r="AN31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
@@ -6062,19 +6129,19 @@
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV31" t="n">
         <v>22</v>
       </c>
       <c r="AW31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX31" t="n">
         <v>2</v>
@@ -6086,7 +6153,7 @@
         <v>25</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-30-2011-12</t>
+          <t>2012-03-30</t>
         </is>
       </c>
     </row>
